--- a/results/Int Task Remove ACC 0.9/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.9/Linea_fi_all.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0010805500982318805 +/- 0.0009773943390045253</t>
+          <t>0.0010314341846758834 +/- 0.0010636742547990006</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.00152259332023571 +/- 0.002201467075738195</t>
+          <t>-0.0014243614931237158 +/- 0.0022448712931289576</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.10604125736738698 +/- 0.005563122572871885</t>
+          <t>-0.10609037328094298 +/- 0.005617280336147643</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.06331325301204824 +/- 0.0049047392215264924</t>
+          <t>0.06337349397590365 +/- 0.004966135866391566</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.022590361445783046 +/- 0.00827409145135182</t>
+          <t>-0.02253012048192763 +/- 0.008256309252535824</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.03229166666666663 +/- 0.0028640258523265445</t>
+          <t>-0.03223684210526312 +/- 0.0029299099157647944</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.0011513157894736392 +/- 0.00082964615956257</t>
+          <t>-0.001096491228070129 +/- 0.0008131796586727558</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.0036184210526315373 +/- 0.0021402654929762416</t>
+          <t>-0.003563596491228027 +/- 0.002126882098823574</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.01289156626506024 +/- 0.006019275179179172</t>
+          <t>-0.012951807228915656 +/- 0.005891615541716217</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.007642971672902144 +/- 0.0015499732763228219</t>
+          <t>0.007696419027258106 +/- 0.001534227695821198</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.03244254409406737 +/- 0.0034806499530015836</t>
+          <t>0.03249599144842332 +/- 0.0034289716584383636</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.0025671641791044754 +/- 0.0035825870301319416</t>
+          <t>0.00268656716417911 +/- 0.0035546210499353328</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.0015522388059701741 +/- 0.000608838150876782</t>
+          <t>-0.0014925373134328512 +/- 0.0006117582546841875</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.0003166226912929337 +/- 0.0004221635883905367</t>
+          <t>-0.00036939313984174493 +/- 0.00047493403693934757</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
